--- a/Lab/Excel_Lookup_Functions_assignment.xlsx
+++ b/Lab/Excel_Lookup_Functions_assignment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6800" tabRatio="500" firstSheet="5" activeTab="8"/>
+    <workbookView windowWidth="19200" windowHeight="6880" tabRatio="500" firstSheet="5" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Employee Dataset" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="325">
   <si>
     <t>Employee Dataset  --  Reference table used across all lookup practice sheets</t>
   </si>
@@ -829,6 +829,9 @@
   </si>
   <si>
     <t>Two-way lookup: Build a dept x metric table and return the Avg Salary for IT using INDEX MATCH MATCH</t>
+  </si>
+  <si>
+    <t>=INDEX('Employee Dataset'!A3:L28,MATCH()</t>
   </si>
   <si>
     <t>Hard</t>
@@ -3681,7 +3684,7 @@
   <sheetData>
     <row r="1" ht="37.5" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3691,7 +3694,7 @@
     </row>
     <row r="2" ht="27.75" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3701,22 +3704,22 @@
     </row>
     <row r="3" ht="21.75" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:6">
@@ -3724,205 +3727,205 @@
         <v>154</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:6">
       <c r="A5" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:6">
       <c r="A6" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:6">
       <c r="A7" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:6">
       <c r="A8" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:6">
       <c r="A9" s="19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:6">
       <c r="A10" s="24" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:6">
       <c r="A11" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:6">
       <c r="A12" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:6">
       <c r="A13" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" ht="15.25"/>
     <row r="15" ht="25.5" customHeight="1" spans="1:6">
       <c r="A15" s="29" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B15" s="29"/>
       <c r="C15" s="29"/>
@@ -3933,7 +3936,7 @@
     <row r="16" ht="21.75" customHeight="1" spans="1:6">
       <c r="A16" s="30"/>
       <c r="B16" s="31" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
@@ -3943,7 +3946,7 @@
     <row r="17" ht="21.75" customHeight="1" spans="1:6">
       <c r="A17" s="32"/>
       <c r="B17" s="33" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -3953,7 +3956,7 @@
     <row r="18" ht="21.75" customHeight="1" spans="1:6">
       <c r="A18" s="34"/>
       <c r="B18" s="35" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
@@ -10226,26 +10229,25 @@
       <c r="B24" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="C24" s="39">
-        <f ca="1">AVERAGEIF('Employee Dataset'!C4:C28,"IT",'Employee Dataset'!E3:E4)</f>
-        <v>76875</v>
+      <c r="C24" s="108" t="s">
+        <v>257</v>
       </c>
       <c r="D24" s="47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" ht="43.5" customHeight="1" spans="1:4">
       <c r="A25" s="46" t="s">
+        <v>259</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>261</v>
+      </c>
+      <c r="D25" s="47" t="s">
         <v>258</v>
-      </c>
-      <c r="B25" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>260</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>257</v>
       </c>
     </row>
   </sheetData>
